--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/OHIO_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/OHIO_2014.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C194">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C201">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C467">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C558">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C784">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C868">
